--- a/Data/FlightPlan/FPL_14OCT26.xlsx
+++ b/Data/FlightPlan/FPL_14OCT26.xlsx
@@ -515,495 +515,498 @@
     <t>VN-A543</t>
   </si>
   <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>THD</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>15:55</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>18:55</t>
+  </si>
+  <si>
+    <t>21:05</t>
+  </si>
+  <si>
+    <t>VN-A544</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>10:25</t>
+  </si>
+  <si>
+    <t>18:50</t>
+  </si>
+  <si>
+    <t>20:50</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>KHV</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>DPS</t>
+  </si>
+  <si>
+    <t>13:35</t>
+  </si>
+  <si>
+    <t>17:25</t>
+  </si>
+  <si>
+    <t>DEL</t>
+  </si>
+  <si>
+    <t>00:05</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>VN-A552</t>
+  </si>
+  <si>
+    <t>15:35</t>
+  </si>
+  <si>
+    <t>01:10</t>
+  </si>
+  <si>
+    <t>VN-A553</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>PUS</t>
+  </si>
+  <si>
+    <t>23:10</t>
+  </si>
+  <si>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>13:05</t>
+  </si>
+  <si>
+    <t>TPE</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>5069 *</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>MFM</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>23:45</t>
+  </si>
+  <si>
+    <t>VVO</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>BLR</t>
+  </si>
+  <si>
+    <t>22:35</t>
+  </si>
+  <si>
+    <t>23:35</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>16:35</t>
+  </si>
+  <si>
+    <t>20:35</t>
+  </si>
+  <si>
+    <t>06:55</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>16:50</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>16:55</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>19:35</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>19:30</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>12:50</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
     <t>09:25</t>
   </si>
   <si>
     <t>13:25</t>
   </si>
   <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>18:50</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>VN-A544</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>10:25</t>
-  </si>
-  <si>
-    <t>THD</t>
-  </si>
-  <si>
-    <t>20:50</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>KHV</t>
-  </si>
-  <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t>14:25</t>
-  </si>
-  <si>
-    <t>14:55</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>DPS</t>
-  </si>
-  <si>
-    <t>13:35</t>
-  </si>
-  <si>
-    <t>17:25</t>
-  </si>
-  <si>
-    <t>DEL</t>
-  </si>
-  <si>
-    <t>00:05</t>
-  </si>
-  <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>VN-A552</t>
-  </si>
-  <si>
-    <t>15:35</t>
-  </si>
-  <si>
-    <t>01:10</t>
-  </si>
-  <si>
-    <t>VN-A553</t>
-  </si>
-  <si>
-    <t>16:15</t>
-  </si>
-  <si>
-    <t>PUS</t>
-  </si>
-  <si>
-    <t>23:10</t>
-  </si>
-  <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>13:05</t>
-  </si>
-  <si>
-    <t>TPE</t>
-  </si>
-  <si>
-    <t>19:00</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>5069 *</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>MFM</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>23:45</t>
-  </si>
-  <si>
-    <t>VVO</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>BLR</t>
-  </si>
-  <si>
-    <t>22:35</t>
-  </si>
-  <si>
-    <t>23:35</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>16:35</t>
-  </si>
-  <si>
-    <t>20:35</t>
-  </si>
-  <si>
-    <t>06:55</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>16:50</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>11:05</t>
-  </si>
-  <si>
-    <t>18:05</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>13:10</t>
-  </si>
-  <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>16:55</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>15:55</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>19:35</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>19:30</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>18:45</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>12:50</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>16:25</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>14:40</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>VN-A648</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>HKT</t>
+  </si>
+  <si>
+    <t>HKG</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>DYG</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>00:10</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>09:50</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>00:25</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>22:45</t>
+  </si>
+  <si>
+    <t>00:55</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>FSZ</t>
+  </si>
+  <si>
+    <t>02:40</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>01:35</t>
+  </si>
+  <si>
+    <t>VN-A663</t>
+  </si>
+  <si>
+    <t>LJG</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>01:20</t>
+  </si>
+  <si>
+    <t>03:55</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>23:15</t>
+  </si>
+  <si>
+    <t>VN-A668</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>VN-A669</t>
   </si>
   <si>
     <t>05:00</t>
   </si>
   <si>
-    <t>08:10</t>
-  </si>
-  <si>
-    <t>10:20</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>16:25</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>14:40</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>VN-A648</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>HKT</t>
-  </si>
-  <si>
-    <t>HKG</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>DYG</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>00:10</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>09:50</t>
-  </si>
-  <si>
-    <t>BMV</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>00:25</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>22:45</t>
-  </si>
-  <si>
-    <t>00:55</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>18:55</t>
-  </si>
-  <si>
-    <t>FSZ</t>
-  </si>
-  <si>
-    <t>02:40</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>23:25</t>
-  </si>
-  <si>
-    <t>01:35</t>
-  </si>
-  <si>
-    <t>VN-A663</t>
-  </si>
-  <si>
-    <t>LJG</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>01:20</t>
-  </si>
-  <si>
-    <t>03:55</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>23:15</t>
-  </si>
-  <si>
-    <t>VN-A668</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>VN-A669</t>
-  </si>
-  <si>
     <t>VN-A672</t>
   </si>
   <si>
@@ -1070,9 +1073,6 @@
     <t>VN-A685</t>
   </si>
   <si>
-    <t>21:05</t>
-  </si>
-  <si>
     <t>00:50</t>
   </si>
   <si>
@@ -1115,6 +1115,9 @@
     <t>VN-A810</t>
   </si>
   <si>
+    <t>17:35</t>
+  </si>
+  <si>
     <t>23:05</t>
   </si>
   <si>
@@ -1166,7 +1169,7 @@
     <t>Total Record(s): 343</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 13, 2026 22:51</t>
+    <t xml:space="preserve">Generated on  Oct 14, 2026 01:27</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -4420,7 +4423,7 @@
         <v>13</v>
       </c>
       <c r="B97" s="7">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c t="s" r="C97" s="7">
         <v>14</v>
@@ -4436,13 +4439,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H97" s="8">
-        <v>89</v>
+        <v>168</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>126</v>
+        <v>68</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -4453,7 +4456,7 @@
         <v>13</v>
       </c>
       <c r="B98" s="7">
-        <v>718</v>
+        <v>351</v>
       </c>
       <c t="s" r="C98" s="7">
         <v>14</v>
@@ -4466,16 +4469,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G98" s="8">
-        <v>89</v>
+        <v>168</v>
       </c>
       <c t="s" r="H98" s="8">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>168</v>
+        <v>87</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>142</v>
+        <v>57</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -4486,7 +4489,7 @@
         <v>13</v>
       </c>
       <c r="B99" s="7">
-        <v>719</v>
+        <v>244</v>
       </c>
       <c t="s" r="C99" s="7">
         <v>14</v>
@@ -4499,16 +4502,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G99" s="8">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c t="s" r="H99" s="8">
-        <v>89</v>
+        <v>169</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>116</v>
+        <v>170</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -4519,7 +4522,7 @@
         <v>13</v>
       </c>
       <c r="B100" s="7">
-        <v>452</v>
+        <v>245</v>
       </c>
       <c t="s" r="C100" s="7">
         <v>14</v>
@@ -4532,16 +4535,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G100" s="8">
-        <v>89</v>
+        <v>169</v>
       </c>
       <c t="s" r="H100" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>39</v>
+        <v>143</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -4552,7 +4555,7 @@
         <v>13</v>
       </c>
       <c r="B101" s="7">
-        <v>441</v>
+        <v>144</v>
       </c>
       <c t="s" r="C101" s="7">
         <v>14</v>
@@ -4565,16 +4568,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G101" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H101" s="8">
         <v>17</v>
       </c>
-      <c t="s" r="H101" s="8">
-        <v>89</v>
-      </c>
       <c t="s" r="I101" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -4585,7 +4588,7 @@
         <v>13</v>
       </c>
       <c r="B102" s="7">
-        <v>442</v>
+        <v>155</v>
       </c>
       <c t="s" r="C102" s="7">
         <v>14</v>
@@ -4598,16 +4601,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G102" s="8">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c t="s" r="H102" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>27</v>
+        <v>174</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -4640,7 +4643,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -4649,10 +4652,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H104" s="8">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="J104" s="7">
         <v>49</v>
@@ -4673,13 +4676,13 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G105" s="8">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c t="s" r="H105" s="8">
         <v>16</v>
@@ -4706,7 +4709,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -4715,7 +4718,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H106" s="8">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c t="s" r="I106" s="7">
         <v>62</v>
@@ -4739,22 +4742,22 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G107" s="8">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c t="s" r="H107" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -4772,7 +4775,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -4781,13 +4784,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H108" s="8">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -4805,22 +4808,22 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G109" s="8">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="H109" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -4853,22 +4856,22 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G111" s="8">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c t="s" r="H111" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -4886,7 +4889,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -4898,7 +4901,7 @@
         <v>71</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c t="s" r="J112" s="7">
         <v>50</v>
@@ -4919,7 +4922,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -4931,10 +4934,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -4967,7 +4970,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -4976,13 +4979,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H115" s="8">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c t="s" r="I115" s="7">
         <v>163</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5000,13 +5003,13 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G116" s="8">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c t="s" r="H116" s="8">
         <v>16</v>
@@ -5015,7 +5018,7 @@
         <v>144</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5033,7 +5036,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5042,7 +5045,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H117" s="8">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c t="s" r="I117" s="7">
         <v>165</v>
@@ -5066,22 +5069,22 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G118" s="8">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c t="s" r="H118" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5114,7 +5117,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5147,7 +5150,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5159,10 +5162,10 @@
         <v>89</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5180,7 +5183,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5195,7 +5198,7 @@
         <v>132</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5228,7 +5231,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5243,7 +5246,7 @@
         <v>116</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5261,7 +5264,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5273,7 +5276,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c t="s" r="J125" s="7">
         <v>95</v>
@@ -5294,7 +5297,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5327,7 +5330,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5336,10 +5339,10 @@
         <v>89</v>
       </c>
       <c t="s" r="H127" s="8">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c t="s" r="J127" s="7">
         <v>125</v>
@@ -5375,7 +5378,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5390,7 +5393,7 @@
         <v>115</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -5408,7 +5411,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5417,10 +5420,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H130" s="8">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c t="s" r="J130" s="7">
         <v>83</v>
@@ -5441,22 +5444,22 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G131" s="8">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c t="s" r="H131" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5482,14 +5485,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B133" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c t="s" r="C133" s="7">
         <v>103</v>
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5501,13 +5504,13 @@
         <v>71</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c t="s" r="J133" s="7">
         <v>47</v>
       </c>
       <c t="s" r="K133" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L133" s="7"/>
       <c t="s" r="M133" s="7">
@@ -5526,7 +5529,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5535,10 +5538,10 @@
         <v>71</v>
       </c>
       <c t="s" r="H134" s="8">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c t="s" r="J134" s="7">
         <v>82</v>
@@ -5559,13 +5562,13 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G135" s="8">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c t="s" r="H135" s="8">
         <v>71</v>
@@ -5574,7 +5577,7 @@
         <v>83</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5592,7 +5595,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5604,10 +5607,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -5625,7 +5628,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5634,13 +5637,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H137" s="8">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5673,7 +5676,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5706,7 +5709,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5739,7 +5742,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -5748,13 +5751,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H141" s="8">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c t="s" r="I141" s="7">
         <v>27</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -5772,22 +5775,22 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G142" s="8">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c t="s" r="H142" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -5820,19 +5823,19 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G144" s="8">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c t="s" r="H144" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="J144" s="7">
         <v>98</v>
@@ -5853,7 +5856,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -5862,10 +5865,10 @@
         <v>22</v>
       </c>
       <c t="s" r="H145" s="8">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c t="s" r="J145" s="7">
         <v>102</v>
@@ -5886,13 +5889,13 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G146" s="8">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c t="s" r="H146" s="8">
         <v>22</v>
@@ -5901,7 +5904,7 @@
         <v>61</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -5919,7 +5922,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -5931,10 +5934,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -5952,7 +5955,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -5961,13 +5964,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H148" s="8">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6000,7 +6003,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6009,7 +6012,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H150" s="8">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c t="s" r="I150" s="7">
         <v>108</v>
@@ -6033,13 +6036,13 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G151" s="8">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c t="s" r="H151" s="8">
         <v>16</v>
@@ -6048,7 +6051,7 @@
         <v>39</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6066,7 +6069,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6075,7 +6078,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H152" s="8">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="I152" s="7">
         <v>33</v>
@@ -6114,7 +6117,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6147,7 +6150,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6159,7 +6162,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c t="s" r="J155" s="7">
         <v>20</v>
@@ -6180,7 +6183,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6213,7 +6216,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6225,10 +6228,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>170</v>
+        <v>238</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6246,7 +6249,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6258,7 +6261,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>236</v>
+        <v>173</v>
       </c>
       <c t="s" r="J158" s="7">
         <v>54</v>
@@ -6279,7 +6282,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6312,7 +6315,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6360,7 +6363,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6375,7 +6378,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6393,7 +6396,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6405,10 +6408,10 @@
         <v>22</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6426,7 +6429,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6441,7 +6444,7 @@
         <v>150</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -6459,7 +6462,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6474,7 +6477,7 @@
         <v>61</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6507,7 +6510,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6540,7 +6543,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6573,7 +6576,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6585,10 +6588,10 @@
         <v>89</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>245</v>
+        <v>172</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -6606,7 +6609,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6654,7 +6657,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6666,10 +6669,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -6687,7 +6690,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -6720,7 +6723,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -6732,7 +6735,7 @@
         <v>124</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="J174" s="7">
         <v>122</v>
@@ -6753,7 +6756,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -6765,10 +6768,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -6801,7 +6804,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -6834,7 +6837,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -6846,7 +6849,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="J178" s="7">
         <v>99</v>
@@ -6867,7 +6870,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -6879,10 +6882,10 @@
         <v>89</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -6900,7 +6903,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -6915,7 +6918,7 @@
         <v>144</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>171</v>
+        <v>252</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -6933,7 +6936,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -6948,7 +6951,7 @@
         <v>132</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -6966,7 +6969,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -6978,10 +6981,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7014,7 +7017,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7029,7 +7032,7 @@
         <v>57</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7047,7 +7050,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7059,7 +7062,7 @@
         <v>89</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c t="s" r="J185" s="7">
         <v>101</v>
@@ -7080,7 +7083,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7092,7 +7095,7 @@
         <v>149</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c t="s" r="J186" s="7">
         <v>26</v>
@@ -7113,7 +7116,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7125,10 +7128,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7161,7 +7164,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7194,7 +7197,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7227,7 +7230,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7239,10 +7242,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7260,7 +7263,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7272,10 +7275,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>173</v>
+        <v>261</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7308,7 +7311,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7323,7 +7326,7 @@
         <v>68</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7341,7 +7344,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7356,7 +7359,7 @@
         <v>97</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7374,7 +7377,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7386,10 +7389,10 @@
         <v>71</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7407,7 +7410,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7422,7 +7425,7 @@
         <v>118</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>245</v>
+        <v>172</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7440,7 +7443,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7452,7 +7455,7 @@
         <v>22</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c t="s" r="J198" s="7">
         <v>94</v>
@@ -7473,7 +7476,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7521,7 +7524,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7533,10 +7536,10 @@
         <v>22</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7554,7 +7557,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7569,7 +7572,7 @@
         <v>164</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7587,7 +7590,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7599,10 +7602,10 @@
         <v>71</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7635,7 +7638,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7647,7 +7650,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c t="s" r="J205" s="7">
         <v>139</v>
@@ -7668,7 +7671,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -7701,7 +7704,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7734,7 +7737,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -7743,10 +7746,10 @@
         <v>71</v>
       </c>
       <c t="s" r="H208" s="8">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c t="s" r="J208" s="7">
         <v>82</v>
@@ -7767,13 +7770,13 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G209" s="8">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c t="s" r="H209" s="8">
         <v>71</v>
@@ -7782,7 +7785,7 @@
         <v>83</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -7808,14 +7811,14 @@
         <v>13</v>
       </c>
       <c r="B211" s="7">
-        <v>120</v>
+        <v>339</v>
       </c>
       <c t="s" r="C211" s="7">
         <v>14</v>
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -7824,13 +7827,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H211" s="8">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>268</v>
+        <v>126</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>45</v>
+        <v>140</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -7841,29 +7844,29 @@
         <v>13</v>
       </c>
       <c r="B212" s="7">
-        <v>127</v>
+        <v>718</v>
       </c>
       <c t="s" r="C212" s="7">
         <v>14</v>
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G212" s="8">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c t="s" r="H212" s="8">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>270</v>
+        <v>142</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -7874,26 +7877,26 @@
         <v>13</v>
       </c>
       <c r="B213" s="7">
-        <v>803</v>
+        <v>719</v>
       </c>
       <c t="s" r="C213" s="7">
         <v>14</v>
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G213" s="8">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c t="s" r="H213" s="8">
-        <v>271</v>
+        <v>89</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>239</v>
+        <v>116</v>
       </c>
       <c t="s" r="J213" s="7">
         <v>272</v>
@@ -7907,29 +7910,29 @@
         <v>13</v>
       </c>
       <c r="B214" s="7">
-        <v>804</v>
+        <v>452</v>
       </c>
       <c t="s" r="C214" s="7">
         <v>14</v>
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G214" s="8">
-        <v>271</v>
+        <v>89</v>
       </c>
       <c t="s" r="H214" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>157</v>
+        <v>39</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -7940,29 +7943,29 @@
         <v>13</v>
       </c>
       <c r="B215" s="7">
-        <v>310</v>
+        <v>441</v>
       </c>
       <c t="s" r="C215" s="7">
         <v>14</v>
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G215" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c t="s" r="H215" s="8">
-        <v>155</v>
+        <v>89</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>62</v>
+        <v>252</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>132</v>
+        <v>179</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -7973,29 +7976,29 @@
         <v>13</v>
       </c>
       <c r="B216" s="7">
-        <v>309</v>
+        <v>442</v>
       </c>
       <c t="s" r="C216" s="7">
         <v>14</v>
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G216" s="8">
-        <v>155</v>
+        <v>89</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>53</v>
+        <v>261</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8106,10 +8109,10 @@
         <v>51</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>245</v>
+        <v>172</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8187,10 +8190,10 @@
         <v>22</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>276</v>
+        <v>170</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8220,10 +8223,10 @@
         <v>149</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -8256,7 +8259,7 @@
         <v>94</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8283,10 +8286,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H226" s="8">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c t="s" r="J226" s="7">
         <v>33</v>
@@ -8313,16 +8316,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G227" s="8">
+        <v>276</v>
+      </c>
+      <c t="s" r="H227" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I227" s="7">
         <v>277</v>
       </c>
-      <c t="s" r="H227" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I227" s="7">
+      <c t="s" r="J227" s="7">
         <v>278</v>
-      </c>
-      <c t="s" r="J227" s="7">
-        <v>279</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8355,7 +8358,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8367,10 +8370,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8388,7 +8391,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8421,7 +8424,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8454,7 +8457,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8469,7 +8472,7 @@
         <v>129</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8487,7 +8490,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8502,7 +8505,7 @@
         <v>282</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8520,7 +8523,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8655,13 +8658,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c t="s" r="H239" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c t="s" r="J239" s="7">
         <v>141</v>
@@ -8769,7 +8772,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G243" s="8">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c t="s" r="H243" s="8">
         <v>71</v>
@@ -8778,7 +8781,7 @@
         <v>164</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -8841,7 +8844,7 @@
         <v>22</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c t="s" r="J245" s="7">
         <v>42</v>
@@ -8904,7 +8907,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H247" s="8">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c t="s" r="I247" s="7">
         <v>291</v>
@@ -9024,7 +9027,7 @@
         <v>23</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9099,13 +9102,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H254" s="8">
-        <v>271</v>
+        <v>297</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9129,7 +9132,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G255" s="8">
-        <v>271</v>
+        <v>297</v>
       </c>
       <c t="s" r="H255" s="8">
         <v>16</v>
@@ -9165,13 +9168,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H256" s="8">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>170</v>
+        <v>238</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9195,7 +9198,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G257" s="8">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c t="s" r="H257" s="8">
         <v>16</v>
@@ -9204,7 +9207,7 @@
         <v>295</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9237,7 +9240,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9252,7 +9255,7 @@
         <v>87</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9270,7 +9273,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9282,7 +9285,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>270</v>
+        <v>304</v>
       </c>
       <c t="s" r="J260" s="7">
         <v>117</v>
@@ -9303,7 +9306,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9312,7 +9315,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>271</v>
+        <v>297</v>
       </c>
       <c t="s" r="I261" s="7">
         <v>143</v>
@@ -9336,19 +9339,19 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>271</v>
+        <v>297</v>
       </c>
       <c t="s" r="H262" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c t="s" r="J262" s="7">
         <v>131</v>
@@ -9369,7 +9372,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9378,7 +9381,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>303</v>
+        <v>168</v>
       </c>
       <c t="s" r="I263" s="7">
         <v>63</v>
@@ -9402,13 +9405,13 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G264" s="8">
-        <v>303</v>
+        <v>168</v>
       </c>
       <c t="s" r="H264" s="8">
         <v>16</v>
@@ -9435,7 +9438,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9468,7 +9471,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9480,10 +9483,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9516,7 +9519,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -9549,7 +9552,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -9561,7 +9564,7 @@
         <v>85</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="J269" s="7">
         <v>108</v>
@@ -9597,7 +9600,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F271" s="7">
         <v>320</v>
@@ -9630,7 +9633,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F272" s="7">
         <v>320</v>
@@ -9663,7 +9666,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F273" s="7">
         <v>320</v>
@@ -9696,7 +9699,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F274" s="7">
         <v>320</v>
@@ -9729,7 +9732,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F275" s="7">
         <v>320</v>
@@ -9762,7 +9765,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F276" s="7">
         <v>320</v>
@@ -9774,10 +9777,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -9810,7 +9813,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -9819,7 +9822,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>271</v>
+        <v>297</v>
       </c>
       <c t="s" r="I278" s="7">
         <v>142</v>
@@ -9843,13 +9846,13 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>271</v>
+        <v>297</v>
       </c>
       <c t="s" r="H279" s="8">
         <v>17</v>
@@ -9876,7 +9879,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -9885,7 +9888,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H280" s="8">
-        <v>303</v>
+        <v>168</v>
       </c>
       <c t="s" r="I280" s="7">
         <v>146</v>
@@ -9909,13 +9912,13 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>303</v>
+        <v>168</v>
       </c>
       <c t="s" r="H281" s="8">
         <v>17</v>
@@ -9942,7 +9945,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
@@ -9954,10 +9957,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -9990,7 +9993,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
@@ -10002,7 +10005,7 @@
         <v>113</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>270</v>
+        <v>304</v>
       </c>
       <c t="s" r="J284" s="7">
         <v>48</v>
@@ -10023,7 +10026,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
@@ -10056,7 +10059,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
@@ -10068,10 +10071,10 @@
         <v>155</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>245</v>
+        <v>172</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10089,7 +10092,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
@@ -10104,7 +10107,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>313</v>
+        <v>174</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10122,7 +10125,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F288" s="7">
         <v>320</v>
@@ -10185,7 +10188,7 @@
         <v>57</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>270</v>
+        <v>304</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10218,7 +10221,7 @@
         <v>99</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10314,10 +10317,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>171</v>
+        <v>252</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>313</v>
+        <v>174</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10428,10 +10431,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>245</v>
+        <v>172</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10461,10 +10464,10 @@
         <v>321</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10539,7 +10542,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H302" s="8">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c t="s" r="I302" s="7">
         <v>325</v>
@@ -10569,7 +10572,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G303" s="8">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c t="s" r="H303" s="8">
         <v>17</v>
@@ -10605,10 +10608,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H304" s="8">
-        <v>271</v>
+        <v>297</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c t="s" r="J304" s="7">
         <v>132</v>
@@ -10635,13 +10638,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>271</v>
+        <v>297</v>
       </c>
       <c t="s" r="H305" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c t="s" r="J305" s="7">
         <v>326</v>
@@ -10677,7 +10680,7 @@
         <v>327</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10719,7 +10722,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H308" s="8">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c t="s" r="I308" s="7">
         <v>115</v>
@@ -10749,13 +10752,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G309" s="8">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c t="s" r="H309" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c t="s" r="J309" s="7">
         <v>158</v>
@@ -10785,13 +10788,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H310" s="8">
-        <v>271</v>
+        <v>297</v>
       </c>
       <c t="s" r="I310" s="7">
         <v>131</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -10815,16 +10818,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G311" s="8">
-        <v>271</v>
+        <v>297</v>
       </c>
       <c t="s" r="H311" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>173</v>
+        <v>261</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -10869,10 +10872,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -10935,7 +10938,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c t="s" r="J315" s="7">
         <v>49</v>
@@ -11004,7 +11007,7 @@
         <v>120</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11034,10 +11037,10 @@
         <v>321</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>236</v>
+        <v>173</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11070,7 +11073,7 @@
         <v>291</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>268</v>
+        <v>331</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11103,7 +11106,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -11112,7 +11115,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c t="s" r="I321" s="7">
         <v>78</v>
@@ -11136,19 +11139,19 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G322" s="8">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c t="s" r="H322" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="J322" s="7">
         <v>127</v>
@@ -11169,7 +11172,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -11184,7 +11187,7 @@
         <v>140</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11202,7 +11205,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -11214,7 +11217,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>276</v>
+        <v>170</v>
       </c>
       <c t="s" r="J324" s="7">
         <v>117</v>
@@ -11235,7 +11238,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -11247,7 +11250,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c t="s" r="J325" s="7">
         <v>130</v>
@@ -11268,7 +11271,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -11280,7 +11283,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c t="s" r="J326" s="7">
         <v>94</v>
@@ -11301,7 +11304,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -11310,7 +11313,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c t="s" r="I327" s="7">
         <v>95</v>
@@ -11334,22 +11337,22 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c t="s" r="H328" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11367,7 +11370,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11379,10 +11382,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11415,7 +11418,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
@@ -11427,10 +11430,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11448,7 +11451,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
@@ -11457,13 +11460,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H332" s="8">
-        <v>303</v>
+        <v>168</v>
       </c>
       <c t="s" r="I332" s="7">
         <v>156</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11481,19 +11484,19 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G333" s="8">
-        <v>303</v>
+        <v>168</v>
       </c>
       <c t="s" r="H333" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>272</v>
+        <v>171</v>
       </c>
       <c t="s" r="J333" s="7">
         <v>21</v>
@@ -11514,7 +11517,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
@@ -11523,7 +11526,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H334" s="8">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c t="s" r="I334" s="7">
         <v>145</v>
@@ -11547,13 +11550,13 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G335" s="8">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c t="s" r="H335" s="8">
         <v>17</v>
@@ -11580,7 +11583,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
@@ -11595,7 +11598,7 @@
         <v>30</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -11613,7 +11616,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F337" s="7">
         <v>321</v>
@@ -11625,10 +11628,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -11661,7 +11664,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -11673,10 +11676,10 @@
         <v>71</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11694,7 +11697,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -11706,7 +11709,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c t="s" r="J340" s="7">
         <v>281</v>
@@ -11727,7 +11730,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -11739,10 +11742,10 @@
         <v>92</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -11760,7 +11763,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -11772,7 +11775,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>272</v>
+        <v>171</v>
       </c>
       <c t="s" r="J342" s="7">
         <v>158</v>
@@ -11793,7 +11796,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -11826,7 +11829,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
@@ -11838,10 +11841,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -11859,7 +11862,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -11868,13 +11871,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c t="s" r="I345" s="7">
         <v>166</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -11892,22 +11895,22 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -11940,7 +11943,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
@@ -11952,7 +11955,7 @@
         <v>113</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c t="s" r="J348" s="7">
         <v>102</v>
@@ -11973,7 +11976,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
@@ -11985,10 +11988,10 @@
         <v>22</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12006,7 +12009,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
@@ -12015,13 +12018,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H350" s="8">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c t="s" r="I350" s="7">
         <v>40</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12039,22 +12042,22 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G351" s="8">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c t="s" r="H351" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12087,7 +12090,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -12120,7 +12123,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
@@ -12132,10 +12135,10 @@
         <v>22</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12168,7 +12171,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
@@ -12180,7 +12183,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="J356" s="7">
         <v>281</v>
@@ -12201,7 +12204,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -12234,7 +12237,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -12249,7 +12252,7 @@
         <v>26</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12267,7 +12270,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -12279,10 +12282,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12308,14 +12311,14 @@
         <v>13</v>
       </c>
       <c r="B361" s="7">
-        <v>350</v>
+        <v>120</v>
       </c>
       <c t="s" r="C361" s="7">
         <v>14</v>
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -12324,13 +12327,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H361" s="8">
-        <v>303</v>
+        <v>17</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>68</v>
+        <v>331</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>139</v>
+        <v>45</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12341,29 +12344,29 @@
         <v>13</v>
       </c>
       <c r="B362" s="7">
-        <v>351</v>
+        <v>127</v>
       </c>
       <c t="s" r="C362" s="7">
         <v>14</v>
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G362" s="8">
-        <v>303</v>
+        <v>17</v>
       </c>
       <c t="s" r="H362" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>87</v>
+        <v>280</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>57</v>
+        <v>304</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12374,14 +12377,14 @@
         <v>13</v>
       </c>
       <c r="B363" s="7">
-        <v>244</v>
+        <v>803</v>
       </c>
       <c t="s" r="C363" s="7">
         <v>14</v>
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -12390,13 +12393,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>177</v>
+        <v>297</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>276</v>
+        <v>241</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>272</v>
+        <v>171</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12407,29 +12410,29 @@
         <v>13</v>
       </c>
       <c r="B364" s="7">
-        <v>245</v>
+        <v>804</v>
       </c>
       <c t="s" r="C364" s="7">
         <v>14</v>
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>177</v>
+        <v>297</v>
       </c>
       <c t="s" r="H364" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>130</v>
+        <v>243</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12440,14 +12443,14 @@
         <v>13</v>
       </c>
       <c r="B365" s="7">
-        <v>144</v>
+        <v>310</v>
       </c>
       <c t="s" r="C365" s="7">
         <v>14</v>
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -12456,13 +12459,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>17</v>
+        <v>155</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>245</v>
+        <v>62</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>236</v>
+        <v>132</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -12473,29 +12476,29 @@
         <v>13</v>
       </c>
       <c r="B366" s="7">
-        <v>155</v>
+        <v>309</v>
       </c>
       <c t="s" r="C366" s="7">
         <v>14</v>
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>17</v>
+        <v>155</v>
       </c>
       <c t="s" r="H366" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>313</v>
+        <v>40</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>353</v>
+        <v>53</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12513,7 +12516,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -12525,7 +12528,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="J367" s="7">
         <v>354</v>
@@ -12546,7 +12549,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -12603,10 +12606,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H370" s="8">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c t="s" r="J370" s="7">
         <v>47</v>
@@ -12633,13 +12636,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G371" s="8">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c t="s" r="H371" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="J371" s="7">
         <v>142</v>
@@ -12669,7 +12672,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c t="s" r="I372" s="7">
         <v>75</v>
@@ -12699,7 +12702,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c t="s" r="H373" s="8">
         <v>16</v>
@@ -12708,7 +12711,7 @@
         <v>76</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>170</v>
+        <v>238</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12735,10 +12738,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H374" s="8">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="J374" s="7">
         <v>122</v>
@@ -12765,16 +12768,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c t="s" r="H375" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -12816,7 +12819,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H377" s="8">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c t="s" r="I377" s="7">
         <v>359</v>
@@ -12846,7 +12849,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G378" s="8">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c t="s" r="H378" s="8">
         <v>16</v>
@@ -12855,7 +12858,7 @@
         <v>80</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -12918,7 +12921,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c t="s" r="J380" s="7">
         <v>50</v>
@@ -12951,7 +12954,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="J381" s="7">
         <v>27</v>
@@ -13029,10 +13032,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="J384" s="7">
         <v>274</v>
@@ -13059,7 +13062,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G385" s="8">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c t="s" r="H385" s="8">
         <v>17</v>
@@ -13068,7 +13071,7 @@
         <v>146</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13146,7 +13149,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>268</v>
+        <v>331</v>
       </c>
       <c t="s" r="J388" s="7">
         <v>359</v>
@@ -13176,7 +13179,7 @@
         <v>60</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>303</v>
+        <v>168</v>
       </c>
       <c t="s" r="I389" s="7">
         <v>363</v>
@@ -13206,13 +13209,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>303</v>
+        <v>168</v>
       </c>
       <c t="s" r="H390" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="J390" s="7">
         <v>141</v>
@@ -13275,7 +13278,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H392" s="8">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c t="s" r="I392" s="7">
         <v>364</v>
@@ -13305,7 +13308,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G393" s="8">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c t="s" r="H393" s="8">
         <v>16</v>
@@ -13347,7 +13350,7 @@
         <v>365</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13377,7 +13380,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c t="s" r="J395" s="7">
         <v>66</v>
@@ -13430,9 +13433,13 @@
       <c t="s" r="J397" s="7">
         <v>115</v>
       </c>
-      <c r="K397" s="7"/>
+      <c t="s" r="K397" s="7">
+        <v>170</v>
+      </c>
       <c r="L397" s="7"/>
-      <c r="M397" s="7"/>
+      <c t="s" r="M397" s="7">
+        <v>251</v>
+      </c>
     </row>
     <row r="398" ht="14.25" customHeight="1">
       <c t="s" r="A398" s="6">
@@ -13458,14 +13465,18 @@
         <v>17</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c t="s" r="J398" s="7">
         <v>49</v>
       </c>
-      <c r="K398" s="7"/>
+      <c t="s" r="K398" s="7">
+        <v>48</v>
+      </c>
       <c r="L398" s="7"/>
-      <c r="M398" s="7"/>
+      <c t="s" r="M398" s="7">
+        <v>282</v>
+      </c>
     </row>
     <row r="399" ht="14.25" customHeight="1">
       <c t="s" r="A399" s="6">
@@ -13496,9 +13507,13 @@
       <c t="s" r="J399" s="7">
         <v>50</v>
       </c>
-      <c r="K399" s="7"/>
+      <c t="s" r="K399" s="7">
+        <v>119</v>
+      </c>
       <c r="L399" s="7"/>
-      <c r="M399" s="7"/>
+      <c t="s" r="M399" s="7">
+        <v>368</v>
+      </c>
     </row>
     <row r="400" ht="15" customHeight="1">
       <c t="s" r="A400" s="6">
@@ -13529,9 +13544,13 @@
       <c t="s" r="J400" s="7">
         <v>84</v>
       </c>
-      <c r="K400" s="7"/>
+      <c t="s" r="K400" s="7">
+        <v>122</v>
+      </c>
       <c r="L400" s="7"/>
-      <c r="M400" s="7"/>
+      <c t="s" r="M400" s="7">
+        <v>300</v>
+      </c>
     </row>
     <row r="401" ht="14.25" customHeight="1">
       <c t="s" r="A401" s="6">
@@ -13557,14 +13576,18 @@
         <v>16</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>368</v>
-      </c>
-      <c r="K401" s="7"/>
+        <v>369</v>
+      </c>
+      <c t="s" r="K401" s="7">
+        <v>166</v>
+      </c>
       <c r="L401" s="7"/>
-      <c r="M401" s="7"/>
+      <c t="s" r="M401" s="7">
+        <v>317</v>
+      </c>
     </row>
     <row r="402" ht="14.25" customHeight="1">
       <c r="A402" s="6"/>
@@ -13593,19 +13616,19 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F403" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G403" s="8">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c t="s" r="H403" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c t="s" r="J403" s="7">
         <v>62</v>
@@ -13626,7 +13649,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F404" s="7">
         <v>330</v>
@@ -13674,22 +13697,22 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F406" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G406" s="8">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c t="s" r="H406" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>170</v>
+        <v>238</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -13707,7 +13730,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F407" s="7">
         <v>330</v>
@@ -13716,10 +13739,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H407" s="8">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c t="s" r="J407" s="7">
         <v>127</v>
@@ -13755,7 +13778,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F409" s="7">
         <v>330</v>
@@ -13788,7 +13811,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F410" s="7">
         <v>330</v>
@@ -13821,7 +13844,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F411" s="7">
         <v>330</v>
@@ -13830,13 +13853,13 @@
         <v>89</v>
       </c>
       <c t="s" r="H411" s="8">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c t="s" r="I411" s="7">
         <v>76</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>353</v>
+        <v>175</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -13854,22 +13877,22 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F412" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G412" s="8">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c t="s" r="H412" s="8">
         <v>89</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -13902,13 +13925,13 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F414" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G414" s="8">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c t="s" r="H414" s="8">
         <v>71</v>
@@ -13950,7 +13973,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F416" s="7">
         <v>330</v>
@@ -13962,10 +13985,10 @@
         <v>89</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -13983,7 +14006,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F417" s="7">
         <v>330</v>
@@ -13992,10 +14015,10 @@
         <v>89</v>
       </c>
       <c t="s" r="H417" s="8">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c t="s" r="J417" s="7">
         <v>290</v>
@@ -14016,22 +14039,22 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F418" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G418" s="8">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c t="s" r="H418" s="8">
         <v>89</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14064,7 +14087,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F420" s="7">
         <v>330</v>
@@ -14073,10 +14096,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H420" s="8">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c t="s" r="J420" s="7">
         <v>295</v>
@@ -14097,22 +14120,22 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F421" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G421" s="8">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c t="s" r="H421" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>268</v>
+        <v>331</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
@@ -14120,7 +14143,7 @@
     </row>
     <row r="422" ht="15.75" customHeight="1">
       <c t="s" r="A422" s="9">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B422" s="9"/>
       <c r="C422" s="9"/>
@@ -14140,7 +14163,7 @@
     <row r="423" ht="65.25" customHeight="1"/>
     <row r="424" ht="16.5" customHeight="1">
       <c t="s" r="A424" s="10">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B424" s="10"/>
       <c r="C424" s="10"/>
@@ -14153,7 +14176,7 @@
       <c r="J424" s="10"/>
       <c r="K424" s="10"/>
       <c t="s" r="L424" s="11">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M424" s="11"/>
       <c r="N424" s="11"/>

--- a/Data/FlightPlan/FPL_14OCT26.xlsx
+++ b/Data/FlightPlan/FPL_14OCT26.xlsx
@@ -182,216 +182,225 @@
     <t>12:05</t>
   </si>
   <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>15:50</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>16:35</t>
+  </si>
+  <si>
+    <t>16:20</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>KIX</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>VN-A500</t>
+  </si>
+  <si>
+    <t>ICN</t>
+  </si>
+  <si>
+    <t>CXR</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>09:50</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>12:25</t>
+  </si>
+  <si>
+    <t>12:49</t>
+  </si>
+  <si>
+    <t>12:55</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>22:55</t>
+  </si>
+  <si>
+    <t>05:35</t>
+  </si>
+  <si>
+    <t>VN-A521</t>
+  </si>
+  <si>
+    <t>09:20</t>
+  </si>
+  <si>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>RMQ</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>19:50</t>
+  </si>
+  <si>
+    <t>NRT</t>
+  </si>
+  <si>
+    <t>00:30</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>VN-A522</t>
+  </si>
+  <si>
+    <t>PQC</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>DLI</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>18:25</t>
+  </si>
+  <si>
+    <t>VN-A526</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>10:39</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>11:55</t>
+  </si>
+  <si>
+    <t>12:23</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>14:50</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>18:35</t>
+  </si>
+  <si>
+    <t>BQS</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>VN-A529</t>
+  </si>
+  <si>
+    <t>07:55</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
+    <t>NGO</t>
+  </si>
+  <si>
+    <t>01:40</t>
+  </si>
+  <si>
+    <t>VN-A530</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>09:04</t>
+  </si>
+  <si>
+    <t>09:30</t>
+  </si>
+  <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>DAD</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>13:43</t>
+  </si>
+  <si>
     <t>14:05</t>
   </si>
   <si>
-    <t>VII</t>
-  </si>
-  <si>
-    <t>15:50</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>16:35</t>
-  </si>
-  <si>
-    <t>16:20</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>18:45</t>
-  </si>
-  <si>
-    <t>KIX</t>
-  </si>
-  <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>08:30</t>
-  </si>
-  <si>
-    <t>VN-A500</t>
-  </si>
-  <si>
-    <t>ICN</t>
-  </si>
-  <si>
-    <t>CXR</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>09:50</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>12:25</t>
-  </si>
-  <si>
-    <t>12:49</t>
-  </si>
-  <si>
-    <t>12:55</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>22:55</t>
-  </si>
-  <si>
-    <t>05:35</t>
-  </si>
-  <si>
-    <t>VN-A521</t>
-  </si>
-  <si>
-    <t>09:20</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>RMQ</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>19:50</t>
-  </si>
-  <si>
-    <t>NRT</t>
-  </si>
-  <si>
-    <t>00:30</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>VN-A522</t>
-  </si>
-  <si>
-    <t>PQC</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>15:05</t>
-  </si>
-  <si>
-    <t>DLI</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>18:25</t>
-  </si>
-  <si>
-    <t>VN-A526</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>10:10</t>
-  </si>
-  <si>
-    <t>10:39</t>
-  </si>
-  <si>
-    <t>10:50</t>
-  </si>
-  <si>
-    <t>11:55</t>
-  </si>
-  <si>
-    <t>12:18</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>14:50</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>18:35</t>
-  </si>
-  <si>
-    <t>BQS</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>VN-A529</t>
-  </si>
-  <si>
-    <t>07:55</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>NGO</t>
-  </si>
-  <si>
-    <t>01:40</t>
-  </si>
-  <si>
-    <t>VN-A530</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>09:04</t>
-  </si>
-  <si>
-    <t>09:30</t>
-  </si>
-  <si>
-    <t>11:40</t>
-  </si>
-  <si>
-    <t>DAD</t>
-  </si>
-  <si>
-    <t>12:10</t>
-  </si>
-  <si>
     <t>15:25</t>
   </si>
   <si>
@@ -479,6 +488,9 @@
     <t>11:10</t>
   </si>
   <si>
+    <t>13:12</t>
+  </si>
+  <si>
     <t>13:15</t>
   </si>
   <si>
@@ -524,7 +536,10 @@
     <t>10:45</t>
   </si>
   <si>
-    <t>12:45</t>
+    <t>13:05</t>
+  </si>
+  <si>
+    <t>13:40</t>
   </si>
   <si>
     <t>15:55</t>
@@ -704,9 +719,6 @@
     <t>VN-A554</t>
   </si>
   <si>
-    <t>13:05</t>
-  </si>
-  <si>
     <t>13:20</t>
   </si>
   <si>
@@ -731,45 +743,51 @@
     <t>10:11</t>
   </si>
   <si>
+    <t>12:50</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>23:45</t>
+  </si>
+  <si>
+    <t>VVO</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>BLR</t>
+  </si>
+  <si>
+    <t>22:35</t>
+  </si>
+  <si>
+    <t>23:35</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
     <t>MFM</t>
   </si>
   <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>23:45</t>
-  </si>
-  <si>
-    <t>VVO</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>BLR</t>
-  </si>
-  <si>
-    <t>22:35</t>
-  </si>
-  <si>
-    <t>23:35</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
     <t>12:15</t>
   </si>
   <si>
@@ -800,7 +818,7 @@
     <t>10:46</t>
   </si>
   <si>
-    <t>12:33</t>
+    <t>12:34</t>
   </si>
   <si>
     <t>16:05</t>
@@ -836,9 +854,6 @@
     <t>08:59</t>
   </si>
   <si>
-    <t>14:10</t>
-  </si>
-  <si>
     <t>VN-A633</t>
   </si>
   <si>
@@ -866,6 +881,9 @@
     <t>VN-A635</t>
   </si>
   <si>
+    <t>13:37</t>
+  </si>
+  <si>
     <t>15:45</t>
   </si>
   <si>
@@ -890,6 +908,9 @@
     <t>11:29</t>
   </si>
   <si>
+    <t>14:01</t>
+  </si>
+  <si>
     <t>VN-A639</t>
   </si>
   <si>
@@ -911,19 +932,13 @@
     <t>10:31</t>
   </si>
   <si>
-    <t>12:50</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
     <t>VN-A641</t>
   </si>
   <si>
     <t>09:16</t>
   </si>
   <si>
-    <t>13:40</t>
+    <t>13:46</t>
   </si>
   <si>
     <t>14:20</t>
@@ -1010,6 +1025,9 @@
     <t>HKT</t>
   </si>
   <si>
+    <t>14:06</t>
+  </si>
+  <si>
     <t>HKG</t>
   </si>
   <si>
@@ -1025,6 +1043,9 @@
     <t>10:21</t>
   </si>
   <si>
+    <t>13:19</t>
+  </si>
+  <si>
     <t>DYG</t>
   </si>
   <si>
@@ -1073,9 +1094,6 @@
     <t>VN-A657</t>
   </si>
   <si>
-    <t>13:04</t>
-  </si>
-  <si>
     <t>22:45</t>
   </si>
   <si>
@@ -1115,6 +1133,9 @@
     <t>LJG</t>
   </si>
   <si>
+    <t>15:02</t>
+  </si>
+  <si>
     <t>PKX</t>
   </si>
   <si>
@@ -1133,6 +1154,9 @@
     <t>11:42</t>
   </si>
   <si>
+    <t>14:56</t>
+  </si>
+  <si>
     <t>20:25</t>
   </si>
   <si>
@@ -1232,9 +1256,6 @@
     <t>10:19</t>
   </si>
   <si>
-    <t>12:56</t>
-  </si>
-  <si>
     <t>00:50</t>
   </si>
   <si>
@@ -1313,6 +1334,9 @@
     <t>09:12</t>
   </si>
   <si>
+    <t>12:59</t>
+  </si>
+  <si>
     <t>NQZ</t>
   </si>
   <si>
@@ -1325,6 +1349,9 @@
     <t>VN-A817</t>
   </si>
   <si>
+    <t>12:46</t>
+  </si>
+  <si>
     <t>23:55</t>
   </si>
   <si>
@@ -1343,7 +1370,7 @@
     <t>Total Record(s): 343</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 14, 2026 11:22</t>
+    <t xml:space="preserve">Generated on  Oct 14, 2026 12:20</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -2864,7 +2891,9 @@
       </c>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
-      <c r="M38" s="7"/>
+      <c t="s" r="M38" s="7">
+        <v>94</v>
+      </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
       <c t="s" r="A39" s="6">
@@ -2893,7 +2922,7 @@
         <v>30</v>
       </c>
       <c t="s" r="J39" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
@@ -2920,13 +2949,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H40" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="I40" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="J40" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
@@ -2950,13 +2979,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G41" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="H41" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I41" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="J41" s="7">
         <v>49</v>
@@ -2992,7 +3021,7 @@
       </c>
       <c r="D43" s="7"/>
       <c t="s" r="E43" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F43" s="7">
         <v>321</v>
@@ -3004,15 +3033,15 @@
         <v>92</v>
       </c>
       <c t="s" r="I43" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="J43" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
       <c t="s" r="M43" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
@@ -3027,7 +3056,7 @@
       </c>
       <c r="D44" s="7"/>
       <c t="s" r="E44" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F44" s="7">
         <v>321</v>
@@ -3039,15 +3068,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I44" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J44" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
       <c t="s" r="M44" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
@@ -3062,7 +3091,7 @@
       </c>
       <c r="D45" s="7"/>
       <c t="s" r="E45" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F45" s="7">
         <v>321</v>
@@ -3074,10 +3103,10 @@
         <v>92</v>
       </c>
       <c t="s" r="I45" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="J45" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
@@ -3091,11 +3120,11 @@
         <v>3525</v>
       </c>
       <c t="s" r="C46" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D46" s="7"/>
       <c t="s" r="E46" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F46" s="7">
         <v>321</v>
@@ -3107,10 +3136,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I46" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="J46" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
@@ -3124,11 +3153,11 @@
         <v>3525</v>
       </c>
       <c t="s" r="C47" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D47" s="7"/>
       <c t="s" r="E47" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F47" s="7">
         <v>321</v>
@@ -3137,13 +3166,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H47" s="8">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c t="s" r="I47" s="7">
         <v>23</v>
       </c>
       <c t="s" r="J47" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
@@ -3176,7 +3205,7 @@
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F49" s="7">
         <v>321</v>
@@ -3188,15 +3217,15 @@
         <v>88</v>
       </c>
       <c t="s" r="I49" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c t="s" r="J49" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
       <c t="s" r="M49" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
@@ -3211,7 +3240,7 @@
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
@@ -3223,7 +3252,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I50" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="J50" s="7">
         <v>35</v>
@@ -3244,7 +3273,7 @@
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F51" s="7">
         <v>321</v>
@@ -3253,10 +3282,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H51" s="8">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c t="s" r="I51" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="J51" s="7">
         <v>90</v>
@@ -3292,7 +3321,7 @@
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
@@ -3301,18 +3330,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H53" s="8">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="I53" s="7">
         <v>72</v>
       </c>
       <c t="s" r="J53" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
       <c t="s" r="M53" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1">
@@ -3327,27 +3356,27 @@
       </c>
       <c r="D54" s="7"/>
       <c t="s" r="E54" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F54" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G54" s="8">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="H54" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I54" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="J54" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
       <c t="s" r="M54" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
@@ -3362,7 +3391,7 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
@@ -3371,17 +3400,19 @@
         <v>17</v>
       </c>
       <c t="s" r="H55" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="I55" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="J55" s="7">
         <v>44</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
-      <c r="M55" s="7"/>
+      <c t="s" r="M55" s="7">
+        <v>128</v>
+      </c>
     </row>
     <row r="56" ht="14.25" customHeight="1">
       <c t="s" r="A56" s="6">
@@ -3395,22 +3426,22 @@
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F56" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G56" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="H56" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I56" s="7">
-        <v>57</v>
+        <v>129</v>
       </c>
       <c t="s" r="J56" s="7">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
@@ -3428,7 +3459,7 @@
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
@@ -3440,10 +3471,10 @@
         <v>71</v>
       </c>
       <c t="s" r="I57" s="7">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c t="s" r="J57" s="7">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
@@ -3461,7 +3492,7 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
@@ -3473,7 +3504,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I58" s="7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c t="s" r="J58" s="7">
         <v>49</v>
@@ -3509,7 +3540,7 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
@@ -3518,18 +3549,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H60" s="8">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c t="s" r="I60" s="7">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
       <c t="s" r="M60" s="7">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
@@ -3544,27 +3575,27 @@
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F61" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G61" s="8">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c t="s" r="H61" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I61" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c t="s" r="J61" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
       <c t="s" r="M61" s="7">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="62" ht="14.25" customHeight="1">
@@ -3579,7 +3610,7 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
@@ -3591,10 +3622,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I62" s="7">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c t="s" r="J62" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
@@ -3614,7 +3645,7 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
@@ -3651,7 +3682,7 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
@@ -3663,13 +3694,13 @@
         <v>46</v>
       </c>
       <c t="s" r="I64" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="J64" s="7">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="K64" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L64" s="7"/>
       <c t="s" r="M64" s="7">
@@ -3688,7 +3719,7 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
@@ -3700,17 +3731,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I65" s="7">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c t="s" r="J65" s="7">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c t="s" r="K65" s="7">
         <v>33</v>
       </c>
       <c r="L65" s="7"/>
       <c t="s" r="M65" s="7">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
@@ -3725,7 +3756,7 @@
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
@@ -3734,13 +3765,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H66" s="8">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c t="s" r="I66" s="7">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c t="s" r="J66" s="7">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
@@ -3758,22 +3789,22 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G67" s="8">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c t="s" r="H67" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -3806,7 +3837,7 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
@@ -3815,18 +3846,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H69" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
       <c t="s" r="M69" s="7">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
@@ -3841,13 +3872,13 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G70" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="H70" s="8">
         <v>17</v>
@@ -3856,12 +3887,12 @@
         <v>82</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
       <c t="s" r="M70" s="7">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="71" ht="14.25" customHeight="1">
@@ -3876,7 +3907,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -3885,20 +3916,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H71" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c t="s" r="J71" s="7">
         <v>42</v>
       </c>
       <c t="s" r="K71" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L71" s="7"/>
       <c t="s" r="M71" s="7">
-        <v>30</v>
+        <v>159</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1">
@@ -3913,29 +3944,29 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G72" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="H72" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c t="s" r="K72" s="7">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="L72" s="7"/>
       <c t="s" r="M72" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
@@ -3950,7 +3981,7 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -3959,13 +3990,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H73" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="I73" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
@@ -3983,13 +4014,13 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G74" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="H74" s="8">
         <v>17</v>
@@ -4031,7 +4062,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -4043,15 +4074,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
       <c t="s" r="M76" s="7">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
@@ -4066,7 +4097,7 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
@@ -4075,17 +4106,19 @@
         <v>16</v>
       </c>
       <c t="s" r="H77" s="8">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
-      <c r="M77" s="7"/>
+      <c t="s" r="M77" s="7">
+        <v>161</v>
+      </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c t="s" r="A78" s="6">
@@ -4099,22 +4132,22 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G78" s="8">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c t="s" r="H78" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -4132,7 +4165,7 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
@@ -4141,13 +4174,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H79" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="I79" s="7">
         <v>47</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
@@ -4165,22 +4198,22 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G80" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="H80" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
@@ -4213,7 +4246,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -4222,18 +4255,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H82" s="8">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>171</v>
+        <v>94</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
       <c t="s" r="M82" s="7">
-        <v>30</v>
+        <v>175</v>
       </c>
     </row>
     <row r="83" ht="14.25" customHeight="1">
@@ -4248,26 +4281,30 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G83" s="8">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c t="s" r="H83" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c t="s" r="J83" s="7">
+        <v>117</v>
+      </c>
+      <c t="s" r="K83" s="7">
+        <v>176</v>
+      </c>
+      <c r="L83" s="7"/>
+      <c t="s" r="M83" s="7">
         <v>116</v>
       </c>
-      <c r="K83" s="7"/>
-      <c r="L83" s="7"/>
-      <c r="M83" s="7"/>
     </row>
     <row r="84" ht="14.25" customHeight="1">
       <c t="s" r="A84" s="6">
@@ -4281,7 +4318,7 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4293,14 +4330,18 @@
         <v>17</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>173</v>
-      </c>
-      <c r="K84" s="7"/>
+        <v>178</v>
+      </c>
+      <c t="s" r="K84" s="7">
+        <v>97</v>
+      </c>
       <c r="L84" s="7"/>
-      <c r="M84" s="7"/>
+      <c t="s" r="M84" s="7">
+        <v>178</v>
+      </c>
     </row>
     <row r="85" ht="15" customHeight="1">
       <c t="s" r="A85" s="6">
@@ -4314,7 +4355,7 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4326,10 +4367,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -4347,7 +4388,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4359,7 +4400,7 @@
         <v>70</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c t="s" r="J86" s="7">
         <v>18</v>
@@ -4395,7 +4436,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4407,15 +4448,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
       <c t="s" r="M88" s="7">
-        <v>180</v>
+        <v>185</v>
       </c>
     </row>
     <row r="89" ht="14.25" customHeight="1">
@@ -4430,7 +4471,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4442,15 +4483,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
       <c t="s" r="M89" s="7">
-        <v>183</v>
+        <v>188</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
@@ -4465,7 +4506,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4480,7 +4521,7 @@
         <v>20</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
@@ -4498,7 +4539,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4510,7 +4551,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c t="s" r="J91" s="7">
         <v>89</v>
@@ -4546,7 +4587,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4555,18 +4596,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H93" s="8">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c t="s" r="I93" s="7">
         <v>26</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
       <c t="s" r="M93" s="7">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="94" ht="14.25" customHeight="1">
@@ -4581,13 +4622,13 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G94" s="8">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c t="s" r="H94" s="8">
         <v>16</v>
@@ -4601,7 +4642,7 @@
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
       <c t="s" r="M94" s="7">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
@@ -4616,7 +4657,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4625,13 +4666,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H95" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
@@ -4649,22 +4690,22 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G96" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="H96" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -4682,7 +4723,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -4691,13 +4732,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H97" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -4715,22 +4756,22 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G98" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="H98" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -4763,7 +4804,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -4772,10 +4813,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H100" s="8">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c t="s" r="J100" s="7">
         <v>44</v>
@@ -4783,7 +4824,7 @@
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
       <c t="s" r="M100" s="7">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="101" ht="14.25" customHeight="1">
@@ -4798,13 +4839,13 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G101" s="8">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c t="s" r="H101" s="8">
         <v>16</v>
@@ -4813,7 +4854,7 @@
         <v>21</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -4831,7 +4872,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -4840,13 +4881,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H102" s="8">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c t="s" r="I102" s="7">
         <v>62</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -4864,22 +4905,22 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G103" s="8">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c t="s" r="H103" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -4897,7 +4938,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -4906,13 +4947,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H104" s="8">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -4930,22 +4971,22 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G105" s="8">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c t="s" r="H105" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -4974,26 +5015,26 @@
         <v>7707</v>
       </c>
       <c t="s" r="C107" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G107" s="8">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c t="s" r="H107" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -5009,11 +5050,11 @@
         <v>7707</v>
       </c>
       <c t="s" r="C108" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -5025,7 +5066,7 @@
         <v>71</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c t="s" r="J108" s="7">
         <v>45</v>
@@ -5046,7 +5087,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -5058,10 +5099,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -5094,7 +5135,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -5103,18 +5144,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H111" s="8">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
       <c t="s" r="M111" s="7">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
@@ -5129,22 +5170,22 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G112" s="8">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c t="s" r="H112" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -5162,7 +5203,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5171,10 +5212,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H113" s="8">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c t="s" r="J113" s="7">
         <v>79</v>
@@ -5195,22 +5236,22 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G114" s="8">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c t="s" r="H114" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -5243,7 +5284,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5255,7 +5296,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="J116" s="7">
         <v>30</v>
@@ -5263,7 +5304,7 @@
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
       <c t="s" r="M116" s="7">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
@@ -5278,7 +5319,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5290,10 +5331,10 @@
         <v>92</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5311,7 +5352,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5323,10 +5364,10 @@
         <v>70</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5359,7 +5400,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5371,15 +5412,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
       <c t="s" r="M120" s="7">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="121" ht="14.25" customHeight="1">
@@ -5394,7 +5435,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5406,10 +5447,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5427,7 +5468,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5460,7 +5501,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5469,13 +5510,13 @@
         <v>92</v>
       </c>
       <c t="s" r="H123" s="8">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5508,7 +5549,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5520,15 +5561,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>231</v>
+        <v>175</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
       <c t="s" r="M125" s="7">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="126" ht="14.25" customHeight="1">
@@ -5543,7 +5584,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5552,10 +5593,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H126" s="8">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c t="s" r="J126" s="7">
         <v>86</v>
@@ -5576,22 +5617,22 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G127" s="8">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c t="s" r="H127" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -5617,14 +5658,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B129" s="7">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c t="s" r="C129" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5636,17 +5677,17 @@
         <v>71</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c t="s" r="J129" s="7">
         <v>41</v>
       </c>
       <c t="s" r="K129" s="7">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="L129" s="7"/>
       <c t="s" r="M129" s="7">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
@@ -5654,14 +5695,14 @@
         <v>13</v>
       </c>
       <c r="B130" s="7">
-        <v>5530</v>
+        <v>5512</v>
       </c>
       <c t="s" r="C130" s="7">
         <v>14</v>
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5670,10 +5711,10 @@
         <v>71</v>
       </c>
       <c t="s" r="H130" s="8">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>217</v>
+        <v>244</v>
       </c>
       <c t="s" r="J130" s="7">
         <v>85</v>
@@ -5687,20 +5728,20 @@
         <v>13</v>
       </c>
       <c r="B131" s="7">
-        <v>5531</v>
+        <v>5513</v>
       </c>
       <c t="s" r="C131" s="7">
         <v>14</v>
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
+        <v>241</v>
+      </c>
+      <c r="F131" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G131" s="8">
         <v>237</v>
-      </c>
-      <c r="F131" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G131" s="8">
-        <v>240</v>
       </c>
       <c t="s" r="H131" s="8">
         <v>71</v>
@@ -5709,7 +5750,7 @@
         <v>86</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5727,7 +5768,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -5739,10 +5780,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -5760,7 +5801,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5769,13 +5810,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H133" s="8">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -5808,7 +5849,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5820,7 +5861,7 @@
         <v>84</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="J135" s="7">
         <v>21</v>
@@ -5828,7 +5869,7 @@
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
       <c t="s" r="M135" s="7">
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="136" ht="14.25" customHeight="1">
@@ -5843,7 +5884,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5855,7 +5896,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="J136" s="7">
         <v>86</v>
@@ -5876,7 +5917,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5885,13 +5926,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H137" s="8">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5909,22 +5950,22 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G138" s="8">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c t="s" r="H138" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5957,27 +5998,27 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G140" s="8">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c t="s" r="H140" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
       <c t="s" r="M140" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="141" ht="14.25" customHeight="1">
@@ -5992,22 +6033,22 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G141" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="H141" s="8">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -6025,16 +6066,16 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G142" s="8">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c t="s" r="H142" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="I142" s="7">
         <v>59</v>
@@ -6058,22 +6099,22 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G143" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="H143" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -6091,7 +6132,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6100,13 +6141,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H144" s="8">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -6139,7 +6180,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6148,10 +6189,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H146" s="8">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c t="s" r="J146" s="7">
         <v>77</v>
@@ -6159,7 +6200,7 @@
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>257</v>
+        <v>263</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6174,13 +6215,13 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G147" s="8">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c t="s" r="H147" s="8">
         <v>16</v>
@@ -6189,7 +6230,7 @@
         <v>32</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6207,7 +6248,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6216,13 +6257,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H148" s="8">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c t="s" r="I148" s="7">
         <v>67</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6255,7 +6296,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6264,7 +6305,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H150" s="8">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c t="s" r="I150" s="7">
         <v>82</v>
@@ -6275,7 +6316,7 @@
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
       <c t="s" r="M150" s="7">
-        <v>262</v>
+        <v>268</v>
       </c>
     </row>
     <row r="151" ht="14.25" customHeight="1">
@@ -6290,19 +6331,19 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G151" s="8">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c t="s" r="H151" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c t="s" r="J151" s="7">
         <v>20</v>
@@ -6310,7 +6351,7 @@
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
       <c t="s" r="M151" s="7">
-        <v>263</v>
+        <v>269</v>
       </c>
     </row>
     <row r="152" ht="14.25" customHeight="1">
@@ -6325,7 +6366,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6334,13 +6375,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H152" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>57</v>
+        <v>129</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6358,22 +6399,22 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G153" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="H153" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6391,7 +6432,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6403,7 +6444,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c t="s" r="J154" s="7">
         <v>49</v>
@@ -6424,7 +6465,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6436,7 +6477,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c t="s" r="J155" s="7">
         <v>79</v>
@@ -6457,7 +6498,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6469,10 +6510,10 @@
         <v>70</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6505,7 +6546,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6514,18 +6555,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H158" s="8">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c t="s" r="I158" s="7">
         <v>39</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
       <c t="s" r="M158" s="7">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
@@ -6540,27 +6581,27 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G159" s="8">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c t="s" r="H159" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
       <c t="s" r="M159" s="7">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1">
@@ -6575,22 +6616,22 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G160" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="H160" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6608,22 +6649,22 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="H161" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="I161" s="7">
         <v>59</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6656,13 +6697,13 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="H163" s="8">
         <v>16</v>
@@ -6671,12 +6712,12 @@
         <v>80</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
       <c t="s" r="M163" s="7">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="164" ht="14.25" customHeight="1">
@@ -6691,7 +6732,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6700,18 +6741,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H164" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
       <c t="s" r="M164" s="7">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1">
@@ -6726,22 +6767,22 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G165" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="H165" s="8">
         <v>92</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>275</v>
+        <v>57</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6759,7 +6800,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6768,10 +6809,10 @@
         <v>92</v>
       </c>
       <c t="s" r="H166" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="J166" s="7">
         <v>33</v>
@@ -6807,7 +6848,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6819,15 +6860,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
       <c t="s" r="M168" s="7">
-        <v>277</v>
+        <v>282</v>
       </c>
     </row>
     <row r="169" ht="14.25" customHeight="1">
@@ -6842,7 +6883,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6854,7 +6895,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c t="s" r="J169" s="7">
         <v>45</v>
@@ -6875,7 +6916,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6884,13 +6925,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H170" s="8">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c t="s" r="I170" s="7">
         <v>64</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6908,22 +6949,22 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G171" s="8">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c t="s" r="H171" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -6956,7 +6997,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -6965,13 +7006,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c t="s" r="I173" s="7">
         <v>39</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -6991,27 +7032,27 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G174" s="8">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c t="s" r="H174" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
       <c t="s" r="M174" s="7">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1">
@@ -7026,7 +7067,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -7038,14 +7079,16 @@
         <v>92</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
-      <c r="M175" s="7"/>
+      <c t="s" r="M175" s="7">
+        <v>32</v>
+      </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
       <c t="s" r="A176" s="6">
@@ -7059,7 +7102,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7071,10 +7114,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -7092,7 +7135,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -7101,13 +7144,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H177" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -7125,22 +7168,22 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G178" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="H178" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -7173,7 +7216,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7182,7 +7225,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H180" s="8">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c t="s" r="I180" s="7">
         <v>52</v>
@@ -7208,26 +7251,28 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G181" s="8">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c t="s" r="H181" s="8">
         <v>92</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>231</v>
+        <v>175</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
-      <c r="M181" s="7"/>
+      <c t="s" r="M181" s="7">
+        <v>290</v>
+      </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
       <c t="s" r="A182" s="6">
@@ -7241,7 +7286,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7250,13 +7295,13 @@
         <v>92</v>
       </c>
       <c t="s" r="H182" s="8">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7274,22 +7319,22 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G183" s="8">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c t="s" r="H183" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7322,7 +7367,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7331,10 +7376,10 @@
         <v>70</v>
       </c>
       <c t="s" r="H185" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c t="s" r="J185" s="7">
         <v>18</v>
@@ -7342,7 +7387,7 @@
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
       <c t="s" r="M185" s="7">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="186" ht="14.25" customHeight="1">
@@ -7357,13 +7402,13 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="H186" s="8">
         <v>16</v>
@@ -7390,7 +7435,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7405,7 +7450,7 @@
         <v>65</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7423,7 +7468,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7435,10 +7480,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7471,7 +7516,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7486,12 +7531,12 @@
         <v>26</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
       <c t="s" r="M190" s="7">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="191" ht="14.25" customHeight="1">
@@ -7506,7 +7551,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7518,15 +7563,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
       <c t="s" r="M191" s="7">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="192" ht="14.25" customHeight="1">
@@ -7541,7 +7586,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7553,14 +7598,16 @@
         <v>71</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
-      <c r="M192" s="7"/>
+      <c t="s" r="M192" s="7">
+        <v>299</v>
+      </c>
     </row>
     <row r="193" ht="14.25" customHeight="1">
       <c t="s" r="A193" s="6">
@@ -7574,7 +7621,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7586,10 +7633,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>57</v>
+        <v>129</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7607,7 +7654,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7616,13 +7663,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H194" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="I194" s="7">
         <v>61</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7640,22 +7687,22 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G195" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="H195" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7688,7 +7735,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7697,18 +7744,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
       <c t="s" r="M197" s="7">
-        <v>294</v>
+        <v>301</v>
       </c>
     </row>
     <row r="198" ht="14.25" customHeight="1">
@@ -7723,27 +7770,27 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
       <c t="s" r="M198" s="7">
-        <v>295</v>
+        <v>302</v>
       </c>
     </row>
     <row r="199" ht="14.25" customHeight="1">
@@ -7758,7 +7805,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7770,10 +7817,10 @@
         <v>71</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7806,7 +7853,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7818,15 +7865,15 @@
         <v>46</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
       <c t="s" r="M201" s="7">
-        <v>298</v>
+        <v>305</v>
       </c>
     </row>
     <row r="202" ht="14.25" customHeight="1">
@@ -7841,7 +7888,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7856,12 +7903,12 @@
         <v>90</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>299</v>
+        <v>306</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -7876,7 +7923,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7888,17 +7935,17 @@
         <v>71</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J203" s="7">
         <v>19</v>
       </c>
       <c t="s" r="K203" s="7">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="L203" s="7"/>
       <c t="s" r="M203" s="7">
-        <v>56</v>
+        <v>244</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
@@ -7906,14 +7953,14 @@
         <v>13</v>
       </c>
       <c r="B204" s="7">
-        <v>5512</v>
+        <v>5530</v>
       </c>
       <c t="s" r="C204" s="7">
         <v>14</v>
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7922,10 +7969,10 @@
         <v>71</v>
       </c>
       <c t="s" r="H204" s="8">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>300</v>
+        <v>222</v>
       </c>
       <c t="s" r="J204" s="7">
         <v>85</v>
@@ -7939,20 +7986,20 @@
         <v>13</v>
       </c>
       <c r="B205" s="7">
-        <v>5513</v>
+        <v>5531</v>
       </c>
       <c t="s" r="C205" s="7">
         <v>14</v>
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G205" s="8">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c t="s" r="H205" s="8">
         <v>71</v>
@@ -7961,7 +8008,7 @@
         <v>86</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>301</v>
+        <v>238</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7994,7 +8041,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8006,15 +8053,15 @@
         <v>92</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
       <c t="s" r="M207" s="7">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="208" ht="14.25" customHeight="1">
@@ -8029,7 +8076,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8038,13 +8085,13 @@
         <v>92</v>
       </c>
       <c t="s" r="H208" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -8064,29 +8111,29 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G209" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="H209" s="8">
         <v>92</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c t="s" r="K209" s="7">
         <v>56</v>
       </c>
       <c r="L209" s="7"/>
       <c t="s" r="M209" s="7">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
@@ -8101,7 +8148,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8116,14 +8163,14 @@
         <v>32</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c t="s" r="K210" s="7">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="L210" s="7"/>
       <c t="s" r="M210" s="7">
-        <v>306</v>
+        <v>311</v>
       </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
@@ -8138,7 +8185,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8147,13 +8194,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H211" s="8">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -8171,22 +8218,22 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G212" s="8">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c t="s" r="H212" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -8219,7 +8266,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8231,7 +8278,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c t="s" r="J214" s="7">
         <v>18</v>
@@ -8239,7 +8286,7 @@
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
       <c t="s" r="M214" s="7">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1">
@@ -8254,7 +8301,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8266,7 +8313,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="J215" s="7">
         <v>20</v>
@@ -8274,7 +8321,7 @@
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
       <c t="s" r="M215" s="7">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="216" ht="14.25" customHeight="1">
@@ -8289,7 +8336,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8301,10 +8348,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8322,7 +8369,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8334,10 +8381,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8370,7 +8417,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8379,10 +8426,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H219" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c t="s" r="J219" s="7">
         <v>56</v>
@@ -8405,22 +8452,22 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G220" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8438,22 +8485,22 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c t="s" r="H221" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8471,7 +8518,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8480,10 +8527,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H222" s="8">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c t="s" r="J222" s="7">
         <v>67</v>
@@ -8504,22 +8551,22 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G223" s="8">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c t="s" r="H223" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8552,7 +8599,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8564,15 +8611,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
       <c t="s" r="M225" s="7">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
@@ -8587,7 +8634,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8599,15 +8646,15 @@
         <v>92</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
       <c t="s" r="M226" s="7">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="227" ht="14.25" customHeight="1">
@@ -8622,7 +8669,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8634,7 +8681,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c t="s" r="J227" s="7">
         <v>55</v>
@@ -8642,7 +8689,7 @@
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
       <c t="s" r="M227" s="7">
-        <v>104</v>
+        <v>142</v>
       </c>
     </row>
     <row r="228" ht="14.25" customHeight="1">
@@ -8657,7 +8704,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8669,17 +8716,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>275</v>
+        <v>57</v>
       </c>
       <c t="s" r="K228" s="7">
         <v>42</v>
       </c>
       <c r="L228" s="7"/>
       <c t="s" r="M228" s="7">
-        <v>211</v>
+        <v>216</v>
       </c>
     </row>
     <row r="229" ht="14.25" customHeight="1">
@@ -8694,7 +8741,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8706,10 +8753,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c t="s" r="K229" s="7">
         <v>60</v>
@@ -8731,7 +8778,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8740,10 +8787,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H230" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c t="s" r="J230" s="7">
         <v>87</v>
@@ -8779,7 +8826,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8788,18 +8835,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H232" s="8">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
       <c t="s" r="M232" s="7">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
@@ -8814,13 +8861,13 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G233" s="8">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c t="s" r="H233" s="8">
         <v>16</v>
@@ -8829,7 +8876,7 @@
         <v>75</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8847,7 +8894,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8859,10 +8906,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8880,7 +8927,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8913,7 +8960,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8925,10 +8972,10 @@
         <v>88</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -8961,27 +9008,27 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G238" s="8">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c t="s" r="H238" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
       <c t="s" r="M238" s="7">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="239" ht="14.25" customHeight="1">
@@ -8996,7 +9043,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9011,7 +9058,7 @@
         <v>30</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -9029,7 +9076,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -9041,10 +9088,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -9077,27 +9124,27 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c t="s" r="H242" s="8">
         <v>71</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
       <c t="s" r="M242" s="7">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
@@ -9112,7 +9159,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9124,10 +9171,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -9145,7 +9192,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9154,7 +9201,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="I244" s="7">
         <v>65</v>
@@ -9178,22 +9225,22 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="H245" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -9211,7 +9258,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9220,10 +9267,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H246" s="8">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c t="s" r="J246" s="7">
         <v>39</v>
@@ -9259,7 +9306,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9268,18 +9315,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>267</v>
+        <v>273</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -9294,26 +9341,28 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c t="s" r="H249" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
-      <c r="M249" s="7"/>
+      <c t="s" r="M249" s="7">
+        <v>338</v>
+      </c>
     </row>
     <row r="250" ht="15" customHeight="1">
       <c t="s" r="A250" s="6">
@@ -9327,7 +9376,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9336,13 +9385,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H250" s="8">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9360,13 +9409,13 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G251" s="8">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c t="s" r="H251" s="8">
         <v>16</v>
@@ -9375,7 +9424,7 @@
         <v>87</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9408,7 +9457,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="F253" s="7">
         <v>320</v>
@@ -9417,18 +9466,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H253" s="8">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
       <c t="s" r="M253" s="7">
-        <v>337</v>
+        <v>343</v>
       </c>
     </row>
     <row r="254" ht="14.25" customHeight="1">
@@ -9443,13 +9492,13 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="F254" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G254" s="8">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c t="s" r="H254" s="8">
         <v>16</v>
@@ -9462,7 +9511,9 @@
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
-      <c r="M254" s="7"/>
+      <c t="s" r="M254" s="7">
+        <v>344</v>
+      </c>
     </row>
     <row r="255" ht="15" customHeight="1">
       <c t="s" r="A255" s="6">
@@ -9476,7 +9527,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="F255" s="7">
         <v>320</v>
@@ -9485,13 +9536,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H255" s="8">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -9509,22 +9560,22 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="F256" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G256" s="8">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c t="s" r="H256" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9557,7 +9608,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9577,7 +9628,7 @@
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
       <c t="s" r="M258" s="7">
-        <v>342</v>
+        <v>349</v>
       </c>
     </row>
     <row r="259" ht="14.25" customHeight="1">
@@ -9592,7 +9643,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9604,15 +9655,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
       <c t="s" r="M259" s="7">
-        <v>344</v>
+        <v>351</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1">
@@ -9627,19 +9678,19 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
+        <v>348</v>
+      </c>
+      <c r="F260" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G260" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H260" s="8">
         <v>341</v>
       </c>
-      <c r="F260" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G260" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H260" s="8">
-        <v>335</v>
-      </c>
       <c t="s" r="I260" s="7">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c t="s" r="J260" s="7">
         <v>78</v>
@@ -9660,22 +9711,22 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
+        <v>348</v>
+      </c>
+      <c r="F261" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G261" s="8">
         <v>341</v>
       </c>
-      <c r="F261" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G261" s="8">
-        <v>335</v>
-      </c>
       <c t="s" r="H261" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9693,7 +9744,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9702,7 +9753,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c t="s" r="I262" s="7">
         <v>63</v>
@@ -9726,13 +9777,13 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c t="s" r="H263" s="8">
         <v>16</v>
@@ -9741,7 +9792,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9759,7 +9810,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -9768,13 +9819,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9792,22 +9843,22 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G265" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="H265" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9840,7 +9891,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -9852,7 +9903,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="J267" s="7">
         <v>77</v>
@@ -9875,7 +9926,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -9884,10 +9935,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H268" s="8">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="J268" s="7">
         <v>67</v>
@@ -9908,22 +9959,22 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G269" s="8">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c t="s" r="H269" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9956,7 +10007,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="F271" s="7">
         <v>320</v>
@@ -9968,15 +10019,15 @@
         <v>92</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
       <c t="s" r="M271" s="7">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="272" ht="14.25" customHeight="1">
@@ -9991,7 +10042,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="F272" s="7">
         <v>320</v>
@@ -10010,7 +10061,9 @@
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
-      <c r="M272" s="7"/>
+      <c t="s" r="M272" s="7">
+        <v>176</v>
+      </c>
     </row>
     <row r="273" ht="14.25" customHeight="1">
       <c t="s" r="A273" s="6">
@@ -10024,7 +10077,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="F273" s="7">
         <v>320</v>
@@ -10033,7 +10086,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H273" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="I273" s="7">
         <v>32</v>
@@ -10057,13 +10110,13 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="F274" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G274" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="H274" s="8">
         <v>17</v>
@@ -10090,7 +10143,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="F275" s="7">
         <v>320</v>
@@ -10102,10 +10155,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -10123,7 +10176,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="F276" s="7">
         <v>320</v>
@@ -10135,10 +10188,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -10171,7 +10224,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -10180,10 +10233,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c t="s" r="J278" s="7">
         <v>30</v>
@@ -10191,7 +10244,7 @@
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
       <c t="s" r="M278" s="7">
-        <v>354</v>
+        <v>275</v>
       </c>
     </row>
     <row r="279" ht="14.25" customHeight="1">
@@ -10206,13 +10259,13 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c t="s" r="H279" s="8">
         <v>17</v>
@@ -10239,7 +10292,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -10251,10 +10304,10 @@
         <v>92</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10272,7 +10325,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -10284,10 +10337,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10305,7 +10358,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
@@ -10317,10 +10370,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10353,7 +10406,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
@@ -10362,10 +10415,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H284" s="8">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c t="s" r="J284" s="7">
         <v>42</v>
@@ -10373,7 +10426,7 @@
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
       <c t="s" r="M284" s="7">
-        <v>358</v>
+        <v>364</v>
       </c>
     </row>
     <row r="285" ht="15" customHeight="1">
@@ -10388,13 +10441,13 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="H285" s="8">
         <v>17</v>
@@ -10403,7 +10456,7 @@
         <v>30</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10421,7 +10474,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
@@ -10430,10 +10483,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H286" s="8">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c t="s" r="J286" s="7">
         <v>64</v>
@@ -10454,13 +10507,13 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c t="s" r="H287" s="8">
         <v>17</v>
@@ -10469,7 +10522,7 @@
         <v>47</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10487,7 +10540,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="F288" s="7">
         <v>320</v>
@@ -10496,13 +10549,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H288" s="8">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -10535,7 +10588,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10544,18 +10597,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H290" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="I290" s="7">
         <v>52</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
       <c t="s" r="M290" s="7">
-        <v>362</v>
+        <v>368</v>
       </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
@@ -10570,29 +10623,29 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G291" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="H291" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c t="s" r="K291" s="7">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="L291" s="7"/>
       <c t="s" r="M291" s="7">
-        <v>300</v>
+        <v>76</v>
       </c>
     </row>
     <row r="292" ht="14.25" customHeight="1">
@@ -10607,7 +10660,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -10616,20 +10669,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H292" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="I292" s="7">
         <v>30</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c t="s" r="K292" s="7">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="L292" s="7"/>
       <c t="s" r="M292" s="7">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="293" ht="14.25" customHeight="1">
@@ -10644,25 +10697,25 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G293" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="H293" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="K293" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L293" s="7"/>
       <c t="s" r="M293" s="7">
@@ -10681,7 +10734,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -10693,17 +10746,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c t="s" r="K294" s="7">
         <v>85</v>
       </c>
       <c r="L294" s="7"/>
       <c t="s" r="M294" s="7">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1">
@@ -10718,7 +10771,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="F295" s="7">
         <v>321</v>
@@ -10730,10 +10783,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -10766,7 +10819,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -10775,17 +10828,19 @@
         <v>17</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
-      <c r="M297" s="7"/>
+      <c t="s" r="M297" s="7">
+        <v>374</v>
+      </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
       <c t="s" r="A298" s="6">
@@ -10799,22 +10854,22 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G298" s="8">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c t="s" r="H298" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10832,7 +10887,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -10841,13 +10896,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H299" s="8">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>301</v>
+        <v>245</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10865,22 +10920,22 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c t="s" r="H300" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10913,7 +10968,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -10922,10 +10977,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H302" s="8">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c t="s" r="J302" s="7">
         <v>55</v>
@@ -10933,7 +10988,7 @@
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
       <c t="s" r="M302" s="7">
-        <v>373</v>
+        <v>380</v>
       </c>
     </row>
     <row r="303" ht="14.25" customHeight="1">
@@ -10948,13 +11003,13 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G303" s="8">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c t="s" r="H303" s="8">
         <v>17</v>
@@ -10963,11 +11018,13 @@
         <v>42</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
-      <c r="M303" s="7"/>
+      <c t="s" r="M303" s="7">
+        <v>381</v>
+      </c>
     </row>
     <row r="304" ht="14.25" customHeight="1">
       <c t="s" r="A304" s="6">
@@ -10981,7 +11038,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -10990,13 +11047,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H304" s="8">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
@@ -11014,13 +11071,13 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c t="s" r="H305" s="8">
         <v>17</v>
@@ -11029,7 +11086,7 @@
         <v>65</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -11047,7 +11104,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -11059,10 +11116,10 @@
         <v>70</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -11095,7 +11152,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -11104,18 +11161,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H308" s="8">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
       <c t="s" r="M308" s="7">
-        <v>171</v>
+        <v>94</v>
       </c>
     </row>
     <row r="309" ht="14.25" customHeight="1">
@@ -11130,22 +11187,22 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G309" s="8">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c t="s" r="H309" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
@@ -11163,7 +11220,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -11172,10 +11229,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H310" s="8">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="J310" s="7">
         <v>65</v>
@@ -11196,22 +11253,22 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G311" s="8">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c t="s" r="H311" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>301</v>
+        <v>245</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -11244,7 +11301,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -11256,15 +11313,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
       <c t="s" r="M313" s="7">
-        <v>379</v>
+        <v>387</v>
       </c>
     </row>
     <row r="314" ht="14.25" customHeight="1">
@@ -11279,7 +11336,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
@@ -11294,12 +11351,12 @@
         <v>29</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
       <c t="s" r="M314" s="7">
-        <v>380</v>
+        <v>388</v>
       </c>
     </row>
     <row r="315" ht="15" customHeight="1">
@@ -11314,7 +11371,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -11326,14 +11383,16 @@
         <v>16</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c t="s" r="J315" s="7">
         <v>44</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
-      <c r="M315" s="7"/>
+      <c t="s" r="M315" s="7">
+        <v>107</v>
+      </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
       <c t="s" r="A316" s="6">
@@ -11347,7 +11406,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11356,13 +11415,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H316" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -11380,22 +11439,22 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G317" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="H317" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11413,7 +11472,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -11422,13 +11481,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H318" s="8">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11446,22 +11505,22 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c t="s" r="H319" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11494,7 +11553,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -11503,7 +11562,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c t="s" r="I321" s="7">
         <v>80</v>
@@ -11514,7 +11573,7 @@
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
       <c t="s" r="M321" s="7">
-        <v>384</v>
+        <v>392</v>
       </c>
     </row>
     <row r="322" ht="14.25" customHeight="1">
@@ -11529,27 +11588,27 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G322" s="8">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c t="s" r="H322" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
       <c t="s" r="M322" s="7">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="323" ht="14.25" customHeight="1">
@@ -11564,7 +11623,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -11573,18 +11632,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H323" s="8">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
       <c t="s" r="M323" s="7">
-        <v>299</v>
+        <v>306</v>
       </c>
     </row>
     <row r="324" ht="14.25" customHeight="1">
@@ -11599,27 +11658,27 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G324" s="8">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c t="s" r="H324" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
       <c t="s" r="M324" s="7">
-        <v>263</v>
+        <v>94</v>
       </c>
     </row>
     <row r="325" ht="15" customHeight="1">
@@ -11634,7 +11693,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -11646,10 +11705,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>231</v>
+        <v>175</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11667,7 +11726,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -11679,10 +11738,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11700,7 +11759,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -11709,13 +11768,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11733,22 +11792,22 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c t="s" r="H328" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11766,7 +11825,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11778,10 +11837,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11814,7 +11873,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
@@ -11826,15 +11885,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
       <c t="s" r="M331" s="7">
-        <v>389</v>
+        <v>397</v>
       </c>
     </row>
     <row r="332" ht="14.25" customHeight="1">
@@ -11849,7 +11908,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
@@ -11858,18 +11917,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H332" s="8">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
       <c t="s" r="M332" s="7">
-        <v>390</v>
+        <v>398</v>
       </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
@@ -11884,19 +11943,19 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G333" s="8">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c t="s" r="H333" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>171</v>
+        <v>94</v>
       </c>
       <c t="s" r="J333" s="7">
         <v>21</v>
@@ -11917,7 +11976,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
@@ -11926,13 +11985,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H334" s="8">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11950,22 +12009,22 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G335" s="8">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c t="s" r="H335" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -11983,7 +12042,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
@@ -11992,13 +12051,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H336" s="8">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -12016,22 +12075,22 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="F337" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G337" s="8">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c t="s" r="H337" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -12064,7 +12123,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -12076,15 +12135,15 @@
         <v>71</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
       <c t="s" r="M339" s="7">
-        <v>298</v>
+        <v>305</v>
       </c>
     </row>
     <row r="340" ht="15" customHeight="1">
@@ -12099,7 +12158,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -12111,15 +12170,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
       <c t="s" r="M340" s="7">
-        <v>266</v>
+        <v>272</v>
       </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
@@ -12134,7 +12193,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -12143,20 +12202,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H341" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c t="s" r="K341" s="7">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="L341" s="7"/>
       <c t="s" r="M341" s="7">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="342" ht="14.25" customHeight="1">
@@ -12171,25 +12230,25 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G342" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="H342" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>171</v>
+        <v>94</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c t="s" r="K342" s="7">
-        <v>231</v>
+        <v>175</v>
       </c>
       <c r="L342" s="7"/>
       <c t="s" r="M342" s="7">
@@ -12208,7 +12267,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -12217,20 +12276,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="J343" s="7">
         <v>45</v>
       </c>
       <c t="s" r="K343" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L343" s="7"/>
       <c t="s" r="M343" s="7">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
@@ -12245,13 +12304,13 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c t="s" r="H344" s="8">
         <v>17</v>
@@ -12278,7 +12337,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -12287,13 +12346,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -12311,22 +12370,22 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12359,22 +12418,22 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="H348" s="8">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12392,22 +12451,22 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12425,22 +12484,22 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="H350" s="8">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c t="s" r="I350" s="7">
         <v>33</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12458,22 +12517,22 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G351" s="8">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c t="s" r="H351" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12506,13 +12565,13 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G353" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="H353" s="8">
         <v>84</v>
@@ -12539,7 +12598,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
@@ -12548,13 +12607,13 @@
         <v>84</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12587,7 +12646,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
@@ -12599,10 +12658,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12622,7 +12681,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -12637,7 +12696,7 @@
         <v>59</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -12655,7 +12714,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -12667,10 +12726,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12688,7 +12747,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -12700,10 +12759,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12736,7 +12795,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -12748,7 +12807,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c t="s" r="J361" s="7">
         <v>39</v>
@@ -12756,7 +12815,7 @@
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
       <c t="s" r="M361" s="7">
-        <v>405</v>
+        <v>413</v>
       </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
@@ -12771,7 +12830,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -12783,15 +12842,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c t="s" r="M362" s="7">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
@@ -12806,7 +12865,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -12815,18 +12874,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>171</v>
+        <v>94</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
       <c t="s" r="M363" s="7">
-        <v>407</v>
+        <v>160</v>
       </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
@@ -12841,22 +12900,22 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c t="s" r="H364" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12874,7 +12933,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -12883,13 +12942,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c t="s" r="I365" s="7">
         <v>62</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -12907,13 +12966,13 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c t="s" r="H366" s="8">
         <v>16</v>
@@ -12940,7 +12999,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -12952,10 +13011,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -12973,7 +13032,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -12982,13 +13041,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H368" s="8">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -13021,7 +13080,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
@@ -13030,10 +13089,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H370" s="8">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c t="s" r="J370" s="7">
         <v>41</v>
@@ -13056,27 +13115,27 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G371" s="8">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c t="s" r="H371" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
       <c t="s" r="M371" s="7">
-        <v>412</v>
+        <v>419</v>
       </c>
     </row>
     <row r="372" ht="14.25" customHeight="1">
@@ -13091,7 +13150,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
@@ -13100,13 +13159,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c t="s" r="I372" s="7">
         <v>77</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -13124,13 +13183,13 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c t="s" r="H373" s="8">
         <v>16</v>
@@ -13139,7 +13198,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -13157,7 +13216,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
@@ -13166,13 +13225,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H374" s="8">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c t="s" r="I374" s="7">
         <v>64</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -13190,22 +13249,22 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c t="s" r="H375" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>301</v>
+        <v>245</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -13238,7 +13297,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -13247,18 +13306,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H377" s="8">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
       <c t="s" r="M377" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="378" ht="14.25" customHeight="1">
@@ -13273,13 +13332,13 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G378" s="8">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c t="s" r="H378" s="8">
         <v>16</v>
@@ -13288,12 +13347,12 @@
         <v>82</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
       <c t="s" r="M378" s="7">
-        <v>415</v>
+        <v>422</v>
       </c>
     </row>
     <row r="379" ht="14.25" customHeight="1">
@@ -13308,7 +13367,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -13317,13 +13376,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H379" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="I379" s="7">
         <v>44</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13341,19 +13400,19 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G380" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="H380" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c t="s" r="J380" s="7">
         <v>45</v>
@@ -13374,7 +13433,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -13389,7 +13448,7 @@
         <v>64</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13407,7 +13466,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -13422,7 +13481,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13455,7 +13514,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -13464,18 +13523,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
       <c t="s" r="M384" s="7">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1">
@@ -13490,22 +13549,22 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G385" s="8">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c t="s" r="H385" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13523,7 +13582,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -13535,10 +13594,10 @@
         <v>66</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13571,7 +13630,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
@@ -13583,15 +13642,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
       <c t="s" r="M388" s="7">
-        <v>419</v>
+        <v>426</v>
       </c>
     </row>
     <row r="389" ht="14.25" customHeight="1">
@@ -13606,7 +13665,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
@@ -13615,18 +13674,18 @@
         <v>58</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
       <c t="s" r="M389" s="7">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="390" ht="15" customHeight="1">
@@ -13641,27 +13700,27 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c t="s" r="H390" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
-        <v>380</v>
+        <v>388</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -13676,7 +13735,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -13688,7 +13747,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c t="s" r="J391" s="7">
         <v>30</v>
@@ -13696,7 +13755,7 @@
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
       <c t="s" r="M391" s="7">
-        <v>295</v>
+        <v>302</v>
       </c>
     </row>
     <row r="392" ht="14.25" customHeight="1">
@@ -13711,7 +13770,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
@@ -13720,13 +13779,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H392" s="8">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>304</v>
+        <v>176</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -13744,19 +13803,19 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G393" s="8">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c t="s" r="H393" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="J393" s="7">
         <v>63</v>
@@ -13777,7 +13836,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
@@ -13789,10 +13848,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13810,7 +13869,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
@@ -13822,7 +13881,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c t="s" r="J395" s="7">
         <v>24</v>
@@ -13854,11 +13913,11 @@
         <v>607</v>
       </c>
       <c t="s" r="C397" s="7">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="F397" s="7">
         <v>330</v>
@@ -13873,14 +13932,14 @@
         <v>68</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="K397" s="7">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="L397" s="7"/>
       <c t="s" r="M397" s="7">
-        <v>424</v>
+        <v>431</v>
       </c>
     </row>
     <row r="398" ht="14.25" customHeight="1">
@@ -13895,7 +13954,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="F398" s="7">
         <v>330</v>
@@ -13907,7 +13966,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c t="s" r="J398" s="7">
         <v>44</v>
@@ -13917,7 +13976,7 @@
       </c>
       <c r="L398" s="7"/>
       <c t="s" r="M398" s="7">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="399" ht="14.25" customHeight="1">
@@ -13932,7 +13991,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="F399" s="7">
         <v>330</v>
@@ -13950,11 +14009,11 @@
         <v>45</v>
       </c>
       <c t="s" r="K399" s="7">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="L399" s="7"/>
       <c t="s" r="M399" s="7">
-        <v>425</v>
+        <v>432</v>
       </c>
     </row>
     <row r="400" ht="15" customHeight="1">
@@ -13969,7 +14028,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="F400" s="7">
         <v>330</v>
@@ -13987,11 +14046,11 @@
         <v>87</v>
       </c>
       <c t="s" r="K400" s="7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L400" s="7"/>
       <c t="s" r="M400" s="7">
-        <v>339</v>
+        <v>346</v>
       </c>
     </row>
     <row r="401" ht="14.25" customHeight="1">
@@ -14006,7 +14065,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="F401" s="7">
         <v>330</v>
@@ -14018,17 +14077,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c t="s" r="K401" s="7">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="L401" s="7"/>
       <c t="s" r="M401" s="7">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="402" ht="14.25" customHeight="1">
@@ -14058,19 +14117,19 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="F403" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G403" s="8">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c t="s" r="H403" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c t="s" r="J403" s="7">
         <v>62</v>
@@ -14091,7 +14150,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="F404" s="7">
         <v>330</v>
@@ -14139,27 +14198,27 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="F406" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G406" s="8">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c t="s" r="H406" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>431</v>
+        <v>438</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -14174,7 +14233,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="F407" s="7">
         <v>330</v>
@@ -14183,13 +14242,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H407" s="8">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>301</v>
+        <v>245</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -14222,7 +14281,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="F409" s="7">
         <v>330</v>
@@ -14242,7 +14301,7 @@
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
       <c t="s" r="M409" s="7">
-        <v>433</v>
+        <v>440</v>
       </c>
     </row>
     <row r="410" ht="15" customHeight="1">
@@ -14257,7 +14316,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="F410" s="7">
         <v>330</v>
@@ -14269,14 +14328,16 @@
         <v>92</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c t="s" r="J410" s="7">
         <v>30</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
-      <c r="M410" s="7"/>
+      <c t="s" r="M410" s="7">
+        <v>441</v>
+      </c>
     </row>
     <row r="411" ht="14.25" customHeight="1">
       <c t="s" r="A411" s="6">
@@ -14290,7 +14351,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="F411" s="7">
         <v>330</v>
@@ -14299,13 +14360,13 @@
         <v>92</v>
       </c>
       <c t="s" r="H411" s="8">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c t="s" r="I411" s="7">
         <v>78</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -14323,22 +14384,22 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="F412" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G412" s="8">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c t="s" r="H412" s="8">
         <v>92</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14371,27 +14432,27 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="F414" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G414" s="8">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c t="s" r="H414" s="8">
         <v>71</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
       <c t="s" r="M414" s="7">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="415" ht="15" customHeight="1">
@@ -14417,11 +14478,11 @@
         <v>1327</v>
       </c>
       <c t="s" r="C416" s="7">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="F416" s="7">
         <v>330</v>
@@ -14433,14 +14494,16 @@
         <v>92</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c t="s" r="J416" s="7">
         <v>83</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
-      <c r="M416" s="7"/>
+      <c t="s" r="M416" s="7">
+        <v>446</v>
+      </c>
     </row>
     <row r="417" ht="14.25" customHeight="1">
       <c t="s" r="A417" s="6">
@@ -14454,7 +14517,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="F417" s="7">
         <v>330</v>
@@ -14463,13 +14526,13 @@
         <v>92</v>
       </c>
       <c t="s" r="H417" s="8">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>275</v>
+        <v>57</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -14487,22 +14550,22 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="F418" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G418" s="8">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c t="s" r="H418" s="8">
         <v>92</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14535,7 +14598,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="F420" s="7">
         <v>330</v>
@@ -14544,18 +14607,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H420" s="8">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
       <c t="s" r="M420" s="7">
-        <v>441</v>
+        <v>450</v>
       </c>
     </row>
     <row r="421" ht="14.25" customHeight="1">
@@ -14570,22 +14633,22 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="F421" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G421" s="8">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c t="s" r="H421" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
@@ -14593,7 +14656,7 @@
     </row>
     <row r="422" ht="15.75" customHeight="1">
       <c t="s" r="A422" s="9">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="B422" s="9"/>
       <c r="C422" s="9"/>
@@ -14613,7 +14676,7 @@
     <row r="423" ht="65.25" customHeight="1"/>
     <row r="424" ht="16.5" customHeight="1">
       <c t="s" r="A424" s="10">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="B424" s="10"/>
       <c r="C424" s="10"/>
@@ -14626,7 +14689,7 @@
       <c r="J424" s="10"/>
       <c r="K424" s="10"/>
       <c t="s" r="L424" s="11">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="M424" s="11"/>
       <c r="N424" s="11"/>
